--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/scenario_long_short_history.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/history/scenario_long_short_history.xlsx
@@ -3402,13 +3402,13 @@
         <v>33</v>
       </c>
       <c r="D140" s="5">
-        <v>-0.002232619267499699</v>
+        <v>0.0005371045914628231</v>
       </c>
       <c r="E140" s="5">
-        <v>0.002991123082016141</v>
+        <v>0.003811878850881144</v>
       </c>
       <c r="F140">
-        <v>-0.00522374234951584</v>
+        <v>-0.003274774259418321</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3422,13 +3422,13 @@
         <v>33</v>
       </c>
       <c r="D141" s="5">
-        <v>0.01179476617453081</v>
+        <v>0.01301885132185224</v>
       </c>
       <c r="E141" s="5">
-        <v>-0.01119439354122361</v>
+        <v>-0.004232721758588063</v>
       </c>
       <c r="F141">
-        <v>0.02298915971575442</v>
+        <v>0.0172515730804403</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3442,13 +3442,13 @@
         <v>33</v>
       </c>
       <c r="D142" s="5">
-        <v>-0.006490809772561651</v>
+        <v>0.0161648933721797</v>
       </c>
       <c r="E142" s="5">
-        <v>0.003996374474777148</v>
+        <v>0.002615845127437425</v>
       </c>
       <c r="F142">
-        <v>-0.0104871842473388</v>
+        <v>0.01354904824474228</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3462,13 +3462,13 @@
         <v>33</v>
       </c>
       <c r="D143" s="5">
-        <v>0.01199458382461762</v>
+        <v>0.009147612472962495</v>
       </c>
       <c r="E143" s="5">
-        <v>0.00427041990943908</v>
+        <v>0.01169928455943325</v>
       </c>
       <c r="F143">
-        <v>0.007724163915178542</v>
+        <v>-0.00255167208647075</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3482,13 +3482,13 @@
         <v>33</v>
       </c>
       <c r="D144" s="5">
-        <v>-0.006728047154883523</v>
+        <v>-0.01682490759355014</v>
       </c>
       <c r="E144" s="5">
-        <v>0.002683035576536446</v>
+        <v>-0.00884597974769675</v>
       </c>
       <c r="F144">
-        <v>-0.009411082731419969</v>
+        <v>-0.007978927845853393</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3502,13 +3502,13 @@
         <v>33</v>
       </c>
       <c r="D145" s="5">
-        <v>0.01499422348053903</v>
+        <v>-0.001907514981062112</v>
       </c>
       <c r="E145" s="5">
-        <v>0.0008316931451827393</v>
+        <v>-0.005458064301539156</v>
       </c>
       <c r="F145">
-        <v>0.01416253033535629</v>
+        <v>0.003550549320477044</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3522,13 +3522,13 @@
         <v>33</v>
       </c>
       <c r="D146" s="5">
-        <v>-0.004978030280254389</v>
+        <v>-0.004718754482781184</v>
       </c>
       <c r="E146" s="5">
-        <v>0.01111436055335762</v>
+        <v>0.007678595362733998</v>
       </c>
       <c r="F146">
-        <v>-0.016092390833612</v>
+        <v>-0.01239734984551518</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -3542,13 +3542,13 @@
         <v>33</v>
       </c>
       <c r="D147" s="5">
-        <v>0.02188463300062084</v>
+        <v>0.03304219760036988</v>
       </c>
       <c r="E147" s="5">
-        <v>0.02846582460793331</v>
+        <v>0.03638192249160061</v>
       </c>
       <c r="F147">
-        <v>-0.006581191607312468</v>
+        <v>-0.00333972489123073</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3562,13 +3562,13 @@
         <v>33</v>
       </c>
       <c r="D148" s="5">
-        <v>0.05577142261318894</v>
+        <v>0.04947560920000061</v>
       </c>
       <c r="E148" s="5">
-        <v>0.04466980102314441</v>
+        <v>0.04394849778622721</v>
       </c>
       <c r="F148">
-        <v>0.01110162159004453</v>
+        <v>0.005527111413773399</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3582,13 +3582,13 @@
         <v>33</v>
       </c>
       <c r="D149" s="5">
-        <v>-0.006799510285875952</v>
+        <v>0.0005960655913197175</v>
       </c>
       <c r="E149" s="5">
-        <v>-0.0006923655320501953</v>
+        <v>-0.004014227299165167</v>
       </c>
       <c r="F149">
-        <v>-0.006107144753825757</v>
+        <v>0.004610292890484885</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3602,13 +3602,13 @@
         <v>33</v>
       </c>
       <c r="D150" s="5">
-        <v>0.02451251290236039</v>
+        <v>0.01535467280833435</v>
       </c>
       <c r="E150" s="5">
-        <v>0.008437233367322819</v>
+        <v>0.007668385597403155</v>
       </c>
       <c r="F150">
-        <v>0.01607527953503757</v>
+        <v>0.007686287210931196</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -3622,13 +3622,13 @@
         <v>33</v>
       </c>
       <c r="D151" s="5">
-        <v>0.02414057744325686</v>
+        <v>0.01783346412265907</v>
       </c>
       <c r="E151" s="5">
-        <v>-0.004828025483967568</v>
+        <v>-0.01290520586950456</v>
       </c>
       <c r="F151">
-        <v>0.02896860292722443</v>
+        <v>0.03073866999216363</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3642,13 +3642,13 @@
         <v>33</v>
       </c>
       <c r="D152" s="5">
-        <v>-0.01449489751872357</v>
+        <v>-0.01681347852464597</v>
       </c>
       <c r="E152" s="5">
-        <v>-0.01471788150730867</v>
+        <v>-0.0126922025600305</v>
       </c>
       <c r="F152">
-        <v>0.0002229839885850987</v>
+        <v>-0.004121275964615477</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3662,13 +3662,13 @@
         <v>33</v>
       </c>
       <c r="D153" s="5">
-        <v>0.01448192368320547</v>
+        <v>0.009188361309371264</v>
       </c>
       <c r="E153" s="5">
-        <v>0.01323960805009612</v>
+        <v>0.008261382538941259</v>
       </c>
       <c r="F153">
-        <v>0.001242315633109352</v>
+        <v>0.0009269787704300047</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3682,13 +3682,13 @@
         <v>33</v>
       </c>
       <c r="D154" s="5">
-        <v>-0.00034638072450341</v>
+        <v>-0.003937650424272729</v>
       </c>
       <c r="E154" s="5">
-        <v>-0.01426646199770902</v>
+        <v>-0.02038549457568094</v>
       </c>
       <c r="F154">
-        <v>0.01392008127320561</v>
+        <v>0.01644784415140822</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -3702,13 +3702,13 @@
         <v>33</v>
       </c>
       <c r="D155" s="5">
-        <v>0.00485817564157274</v>
+        <v>0.009909885471831102</v>
       </c>
       <c r="E155" s="5">
-        <v>-0.001861139513109388</v>
+        <v>-0.008829561615813211</v>
       </c>
       <c r="F155">
-        <v>0.006719315154682128</v>
+        <v>0.01873944708764431</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3722,13 +3722,13 @@
         <v>33</v>
       </c>
       <c r="D156" s="5">
-        <v>-0.009116709489909702</v>
+        <v>-0.007105223383377973</v>
       </c>
       <c r="E156" s="5">
-        <v>-0.03378893957465494</v>
+        <v>-0.02041787659477016</v>
       </c>
       <c r="F156">
-        <v>0.02467223008474523</v>
+        <v>0.01331265321139219</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3742,13 +3742,13 @@
         <v>33</v>
       </c>
       <c r="D157" s="5">
-        <v>-0.02631080376109236</v>
+        <v>-0.02344053312756439</v>
       </c>
       <c r="E157" s="5">
-        <v>-0.01701740481522478</v>
+        <v>-0.02321725266489736</v>
       </c>
       <c r="F157">
-        <v>-0.009293398945867583</v>
+        <v>-0.000223280462667029</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3762,13 +3762,13 @@
         <v>33</v>
       </c>
       <c r="D158" s="5">
-        <v>0.01761308733698556</v>
+        <v>0.006380306888061861</v>
       </c>
       <c r="E158" s="5">
-        <v>0.01073226331269732</v>
+        <v>-0.000795370870679767</v>
       </c>
       <c r="F158">
-        <v>0.00688082402428824</v>
+        <v>0.007175677758741628</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -3782,13 +3782,13 @@
         <v>33</v>
       </c>
       <c r="D159" s="5">
-        <v>-0.03931141432781873</v>
+        <v>-0.03422739712949305</v>
       </c>
       <c r="E159" s="5">
-        <v>-0.04609202615534878</v>
+        <v>-0.02872888699292137</v>
       </c>
       <c r="F159">
-        <v>0.00678061182753005</v>
+        <v>-0.005498510136571683</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3802,13 +3802,13 @@
         <v>33</v>
       </c>
       <c r="D160" s="5">
-        <v>0.007122875388403473</v>
+        <v>0.006828986337754764</v>
       </c>
       <c r="E160" s="5">
-        <v>0.02178691134461181</v>
+        <v>0.013446357477457</v>
       </c>
       <c r="F160">
-        <v>-0.01466403595620833</v>
+        <v>-0.006617371139702235</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -3822,13 +3822,13 @@
         <v>33</v>
       </c>
       <c r="D161" s="5">
-        <v>-0.00409859299039747</v>
+        <v>0.007053819609722773</v>
       </c>
       <c r="E161" s="5">
-        <v>-0.01203969865172918</v>
+        <v>-0.01540661390839984</v>
       </c>
       <c r="F161">
-        <v>0.007941105661331712</v>
+        <v>0.02246043351812261</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3842,13 +3842,13 @@
         <v>33</v>
       </c>
       <c r="D162" s="5">
-        <v>-0.007079075067114646</v>
+        <v>0.001397389034164583</v>
       </c>
       <c r="E162" s="5">
-        <v>0.02120257607802276</v>
+        <v>0.006367797504881628</v>
       </c>
       <c r="F162">
-        <v>-0.02828165114513741</v>
+        <v>-0.004970408470717046</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -3862,13 +3862,13 @@
         <v>34</v>
       </c>
       <c r="D163" s="5">
-        <v>-0.002232619267499699</v>
+        <v>0.004013232048087302</v>
       </c>
       <c r="E163" s="5">
-        <v>0.002991123082016141</v>
+        <v>0.006531263834735806</v>
       </c>
       <c r="F163">
-        <v>-0.00522374234951584</v>
+        <v>-0.002518031786648505</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3882,13 +3882,13 @@
         <v>34</v>
       </c>
       <c r="D164" s="5">
-        <v>0.009447758874778563</v>
+        <v>0.01460838520886835</v>
       </c>
       <c r="E164" s="5">
-        <v>-0.01969320750763645</v>
+        <v>-0.001068528501853588</v>
       </c>
       <c r="F164">
-        <v>0.02914096638241501</v>
+        <v>0.01567691371072194</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -3902,13 +3902,13 @@
         <v>34</v>
       </c>
       <c r="D165" s="5">
-        <v>-0.00884702471643763</v>
+        <v>0.01637113528519744</v>
       </c>
       <c r="E165" s="5">
-        <v>-0.01078309843396509</v>
+        <v>0.001657155579506821</v>
       </c>
       <c r="F165">
-        <v>0.001936073717527463</v>
+        <v>0.01471397970569062</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3922,13 +3922,13 @@
         <v>34</v>
       </c>
       <c r="D166" s="5">
-        <v>0.02574248547327427</v>
+        <v>0.01428554697063646</v>
       </c>
       <c r="E166" s="5">
-        <v>-0.001243063372538464</v>
+        <v>0.008173143385186968</v>
       </c>
       <c r="F166">
-        <v>0.02698554884581274</v>
+        <v>0.006112403585449492</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -3942,13 +3942,13 @@
         <v>34</v>
       </c>
       <c r="D167" s="5">
-        <v>-0.008401486048657236</v>
+        <v>-0.02309670932252277</v>
       </c>
       <c r="E167" s="5">
-        <v>-0.003663868188235151</v>
+        <v>-0.01137187326751899</v>
       </c>
       <c r="F167">
-        <v>-0.004737617860422085</v>
+        <v>-0.01172483605500379</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3962,13 +3962,13 @@
         <v>34</v>
       </c>
       <c r="D168" s="5">
-        <v>0.008668412638395843</v>
+        <v>-0.01087176599158558</v>
       </c>
       <c r="E168" s="5">
-        <v>-0.004394470747726617</v>
+        <v>0.003543221051246241</v>
       </c>
       <c r="F168">
-        <v>0.01306288338612246</v>
+        <v>-0.01441498704283183</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3982,13 +3982,13 @@
         <v>34</v>
       </c>
       <c r="D169" s="5">
-        <v>-0.004978030280254389</v>
+        <v>-0.004718754482781184</v>
       </c>
       <c r="E169" s="5">
-        <v>-0.004963339791493141</v>
+        <v>0.009912039292718647</v>
       </c>
       <c r="F169">
-        <v>-1.469048876124798E-05</v>
+        <v>-0.01463079377549983</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4002,13 +4002,13 @@
         <v>34</v>
       </c>
       <c r="D170" s="5">
-        <v>0.03213423869507407</v>
+        <v>0.02582094043822173</v>
       </c>
       <c r="E170" s="5">
-        <v>0.03000065287461495</v>
+        <v>0.03638192249160061</v>
       </c>
       <c r="F170">
-        <v>0.002133585820459118</v>
+        <v>-0.01056098205337888</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4022,13 +4022,13 @@
         <v>34</v>
       </c>
       <c r="D171" s="5">
-        <v>0.05944761294321912</v>
+        <v>0.05801787150903686</v>
       </c>
       <c r="E171" s="5">
-        <v>0.04440124061767146</v>
+        <v>0.04519887262324324</v>
       </c>
       <c r="F171">
-        <v>0.01504637232554765</v>
+        <v>0.01281899888579362</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4042,13 +4042,13 @@
         <v>34</v>
       </c>
       <c r="D172" s="5">
-        <v>-0.00297605330585816</v>
+        <v>-0.006104540589164787</v>
       </c>
       <c r="E172" s="5">
-        <v>-0.008728409117176036</v>
+        <v>-0.00483530793313918</v>
       </c>
       <c r="F172">
-        <v>0.005752355811317876</v>
+        <v>-0.001269232656025607</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4062,13 +4062,13 @@
         <v>34</v>
       </c>
       <c r="D173" s="5">
-        <v>0.02921998984223033</v>
+        <v>0.01834117375661897</v>
       </c>
       <c r="E173" s="5">
-        <v>0.006389222544242862</v>
+        <v>0.01371764832937762</v>
       </c>
       <c r="F173">
-        <v>0.02283076729798746</v>
+        <v>0.004623525427241353</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4082,13 +4082,13 @@
         <v>34</v>
       </c>
       <c r="D174" s="5">
-        <v>0.02059467840429502</v>
+        <v>0.009772219809626751</v>
       </c>
       <c r="E174" s="5">
-        <v>-0.01589433371149945</v>
+        <v>-0.0125952437439432</v>
       </c>
       <c r="F174">
-        <v>0.03648901211579447</v>
+        <v>0.02236746355356995</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4102,13 +4102,13 @@
         <v>34</v>
       </c>
       <c r="D175" s="5">
-        <v>-0.01735283175488666</v>
+        <v>-0.01736960446431545</v>
       </c>
       <c r="E175" s="5">
-        <v>-0.008958483539669921</v>
+        <v>-0.01008052451211664</v>
       </c>
       <c r="F175">
-        <v>-0.008394348215216738</v>
+        <v>-0.007289079952198805</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4122,13 +4122,13 @@
         <v>34</v>
       </c>
       <c r="D176" s="5">
-        <v>0.01407704346498004</v>
+        <v>-0.0105212913242529</v>
       </c>
       <c r="E176" s="5">
-        <v>0.02657043059831708</v>
+        <v>0.02024550399819532</v>
       </c>
       <c r="F176">
-        <v>-0.01249338713333704</v>
+        <v>-0.03076679532244822</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4142,13 +4142,13 @@
         <v>34</v>
       </c>
       <c r="D177" s="5">
-        <v>0.008911075933942574</v>
+        <v>-0.007371145303538477</v>
       </c>
       <c r="E177" s="5">
-        <v>-0.01788429237896856</v>
+        <v>-0.01059580591974121</v>
       </c>
       <c r="F177">
-        <v>0.02679536831291114</v>
+        <v>0.003224660616202733</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4162,13 +4162,13 @@
         <v>34</v>
       </c>
       <c r="D178" s="5">
-        <v>-0.001079412020190949</v>
+        <v>-0.0008395440246518217</v>
       </c>
       <c r="E178" s="5">
-        <v>-0.006903937743061263</v>
+        <v>-0.001931917713198389</v>
       </c>
       <c r="F178">
-        <v>0.005824525722870314</v>
+        <v>0.001092373688546568</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4182,13 +4182,13 @@
         <v>34</v>
       </c>
       <c r="D179" s="5">
-        <v>-0.02154288978894124</v>
+        <v>-0.005869875400250228</v>
       </c>
       <c r="E179" s="5">
-        <v>-0.03395899311389639</v>
+        <v>-0.01940366231365234</v>
       </c>
       <c r="F179">
-        <v>0.01241610332495514</v>
+        <v>0.01353378691340211</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4202,13 +4202,13 @@
         <v>34</v>
       </c>
       <c r="D180" s="5">
-        <v>-0.01704727301133413</v>
+        <v>-0.009855773364384075</v>
       </c>
       <c r="E180" s="5">
-        <v>-0.02933797689804865</v>
+        <v>-0.02573382561590415</v>
       </c>
       <c r="F180">
-        <v>0.01229070388671452</v>
+        <v>0.01587805225152007</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -4222,13 +4222,13 @@
         <v>34</v>
       </c>
       <c r="D181" s="5">
-        <v>0.02935220011160959</v>
+        <v>-0.00849143338592342</v>
       </c>
       <c r="E181" s="5">
-        <v>-0.002746741352071588</v>
+        <v>0.004709541186902742</v>
       </c>
       <c r="F181">
-        <v>0.03209894146368118</v>
+        <v>-0.01320097457282616</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4242,13 +4242,13 @@
         <v>34</v>
       </c>
       <c r="D182" s="5">
-        <v>-0.03140002299790319</v>
+        <v>-0.02895603801333147</v>
       </c>
       <c r="E182" s="5">
-        <v>-0.03008123346170249</v>
+        <v>-0.02055310436885905</v>
       </c>
       <c r="F182">
-        <v>-0.001318789536200696</v>
+        <v>-0.008402933644472425</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4262,13 +4262,13 @@
         <v>34</v>
       </c>
       <c r="D183" s="5">
-        <v>0.02894045318227326</v>
+        <v>0.01911637841431823</v>
       </c>
       <c r="E183" s="5">
-        <v>0.00382621543809861</v>
+        <v>0.007547930115593133</v>
       </c>
       <c r="F183">
-        <v>0.02511423774417465</v>
+        <v>0.0115684482987251</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4282,13 +4282,13 @@
         <v>34</v>
       </c>
       <c r="D184" s="5">
-        <v>-0.01878439895554052</v>
+        <v>-0.001259245329660846</v>
       </c>
       <c r="E184" s="5">
-        <v>-0.01071180581950086</v>
+        <v>-0.02297099287760226</v>
       </c>
       <c r="F184">
-        <v>-0.00807259313603966</v>
+        <v>0.02171174754794142</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4302,13 +4302,13 @@
         <v>34</v>
       </c>
       <c r="D185" s="5">
-        <v>0.001716306596578913</v>
+        <v>0.001383706896237246</v>
       </c>
       <c r="E185" s="5">
-        <v>0.001967369502423375</v>
+        <v>0.006131523732501609</v>
       </c>
       <c r="F185">
-        <v>-0.0002510629058444613</v>
+        <v>-0.004747816836264363</v>
       </c>
     </row>
   </sheetData>
